--- a/Catch and index models/JABBA_macarellus/jabba_tornado_sensibilidade.xlsx
+++ b/Catch and index models/JABBA_macarellus/jabba_tornado_sensibilidade.xlsx
@@ -49,19 +49,19 @@
     <t>Indice usado</t>
   </si>
   <si>
+    <t>J12_soC2_historico</t>
+  </si>
+  <si>
+    <t>J1_C1_ingenuo</t>
+  </si>
+  <si>
     <t>J2_C2C3_nominal</t>
   </si>
   <si>
     <t>J18_BASE_C2C6</t>
   </si>
   <si>
-    <t>J12_soC2_historico</t>
-  </si>
-  <si>
     <t>J5_soC5_curto</t>
-  </si>
-  <si>
-    <t>J1_C1_ingenuo</t>
   </si>
   <si>
     <t>J9_soC3_curto</t>
@@ -486,10 +486,10 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>4027.771232382639</v>
+        <v>3818.564722567396</v>
       </c>
       <c r="F2">
-        <v>22.15938695463458</v>
+        <v>21.79979897365868</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -506,10 +506,10 @@
         <v>11</v>
       </c>
       <c r="E3">
-        <v>2119.049295383454</v>
+        <v>3056.430257368051</v>
       </c>
       <c r="F3">
-        <v>-35.73076822996159</v>
+        <v>-2.509812463217696</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -526,10 +526,10 @@
         <v>12</v>
       </c>
       <c r="E4">
-        <v>3340.838090323099</v>
+        <v>2764.218866491746</v>
       </c>
       <c r="F4">
-        <v>1.32520182561125</v>
+        <v>-11.83040573644563</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -546,10 +546,10 @@
         <v>13</v>
       </c>
       <c r="E5">
-        <v>3540.94085454916</v>
+        <v>2165.232021973961</v>
       </c>
       <c r="F5">
-        <v>7.394173868823155</v>
+        <v>-30.93613853153635</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -566,10 +566,10 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>3582.736364755819</v>
+        <v>2147.255756195835</v>
       </c>
       <c r="F6">
-        <v>8.661801449866598</v>
+        <v>-31.50952296185202</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -586,10 +586,10 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <v>3604.71273960018</v>
+        <v>2141.147939962468</v>
       </c>
       <c r="F7">
-        <v>9.328328996637001</v>
+        <v>-31.70434244075088</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -606,10 +606,10 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>3639.335035052304</v>
+        <v>3856.77349636981</v>
       </c>
       <c r="F8">
-        <v>10.37839816476396</v>
+        <v>23.01853462599958</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -626,10 +626,10 @@
         <v>18</v>
       </c>
       <c r="E9">
-        <v>2132.736716058769</v>
+        <v>2519.881441031651</v>
       </c>
       <c r="F9">
-        <v>-35.31563866519294</v>
+        <v>-19.6239751702437</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -646,10 +646,10 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>5850.533385420926</v>
+        <v>5196.993139303906</v>
       </c>
       <c r="F10">
-        <v>77.44244409279962</v>
+        <v>65.76718364723936</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -666,10 +666,10 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>2951.33419215964</v>
+        <v>2853.138864567934</v>
       </c>
       <c r="F11">
-        <v>-10.48816955793219</v>
+        <v>-8.994146912178287</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -686,10 +686,10 @@
         <v>22</v>
       </c>
       <c r="E12">
-        <v>3491.48202773739</v>
+        <v>3249.56937857029</v>
       </c>
       <c r="F12">
-        <v>5.894123440376356</v>
+        <v>3.650697530852875</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -706,10 +706,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>2.616066387877068</v>
+        <v>2.613770362584439</v>
       </c>
       <c r="F13">
-        <v>35.59518149046522</v>
+        <v>35.98466422972738</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -723,13 +723,13 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>1.925077181295874</v>
+        <v>1.70348958600296</v>
       </c>
       <c r="F14">
-        <v>-0.2199672796555227</v>
+        <v>-11.3738288996433</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -743,13 +743,13 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E15">
-        <v>1.921351323926983</v>
+        <v>0.6897639458397753</v>
       </c>
       <c r="F15">
-        <v>-0.4130848199761541</v>
+        <v>-64.11417012164412</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -763,13 +763,13 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>1.830534009177713</v>
+        <v>0.6489144011979358</v>
       </c>
       <c r="F16">
-        <v>-5.120301094367821</v>
+        <v>-66.2394186482841</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -783,13 +783,13 @@
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E17">
-        <v>0.5315885289768161</v>
+        <v>0.613133927057994</v>
       </c>
       <c r="F17">
-        <v>-72.44686014128477</v>
+        <v>-68.10094245754846</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -803,13 +803,13 @@
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18">
-        <v>1.932444738463548</v>
+        <v>1.924438693289885</v>
       </c>
       <c r="F18">
-        <v>0.1619057706315807</v>
+        <v>0.1213240779740599</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -823,13 +823,13 @@
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19">
-        <v>1.939723513376226</v>
+        <v>1.933073278828853</v>
       </c>
       <c r="F19">
-        <v>0.5391770852612026</v>
+        <v>0.570549163730419</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -846,10 +846,10 @@
         <v>18</v>
       </c>
       <c r="E20">
-        <v>0.8677861881438657</v>
+        <v>1.931658377597843</v>
       </c>
       <c r="F20">
-        <v>-55.02116222219671</v>
+        <v>0.4969371618608837</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -866,10 +866,10 @@
         <v>19</v>
       </c>
       <c r="E21">
-        <v>1.940207361836288</v>
+        <v>1.944541440184515</v>
       </c>
       <c r="F21">
-        <v>0.5642557759473587</v>
+        <v>1.167194566710682</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -886,10 +886,10 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.863967829479363</v>
+        <v>1.866784333363605</v>
       </c>
       <c r="F22">
-        <v>-3.387369180739781</v>
+        <v>-2.878215930660404</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -906,10 +906,10 @@
         <v>22</v>
       </c>
       <c r="E23">
-        <v>1.944723529694755</v>
+        <v>1.944175626174088</v>
       </c>
       <c r="F23">
-        <v>0.7983364564866811</v>
+        <v>1.14816263640395</v>
       </c>
     </row>
     <row r="24" spans="1:6">
